--- a/b.xlsx
+++ b/b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ali-Amir\Desktop\Practice 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC747D3-6198-400C-9C76-3CC78F315EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A916AC5C-C54F-4BE2-9FC6-5962FA0981D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>a</t>
   </si>
@@ -34,6 +34,18 @@
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>faeW</t>
+  </si>
+  <si>
+    <t>FFQ</t>
+  </si>
+  <si>
+    <t>3Q3</t>
+  </si>
+  <si>
+    <t>W3W</t>
   </si>
 </sst>
 </file>
@@ -351,10 +363,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -365,7 +377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -374,6 +386,22 @@
       </c>
       <c r="C2">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/b.xlsx
+++ b/b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ali-Amir\Desktop\Practice 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A916AC5C-C54F-4BE2-9FC6-5962FA0981D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69BC3E5-E130-4590-9BF8-828B9424126D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>a</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>3Q3</t>
-  </si>
-  <si>
-    <t>W3W</t>
   </si>
 </sst>
 </file>
@@ -388,11 +385,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N5" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="L6" t="s">
         <v>3</v>
